--- a/figures/timeline-sea/TimelineJS3 Template_Seattle DWO_May 2026.xlsx
+++ b/figures/timeline-sea/TimelineJS3 Template_Seattle DWO_May 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lians\git\dwbr-website\figures\timeline-sea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67599B92-4D58-410C-B57B-637714910C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64306BEA-21FB-436A-A8AD-3FB5B0DD219D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -254,7 +254,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>Year</t>
   </si>
@@ -403,13 +403,16 @@
     <t>img/photo_3.jpg</t>
   </si>
   <si>
-    <t>img/photo_4.jpg</t>
-  </si>
-  <si>
     <t>img/photo_7.jpg</t>
   </si>
   <si>
     <t>img/photo_8.jpg</t>
+  </si>
+  <si>
+    <t>img/photo_5.jpg</t>
+  </si>
+  <si>
+    <t>img/photo_4.png</t>
   </si>
 </sst>
 </file>
@@ -1124,9 +1127,6 @@
       <c r="K2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="20" t="s">
-        <v>47</v>
-      </c>
       <c r="M2" s="21"/>
       <c r="N2" s="21"/>
       <c r="O2" s="12"/>
@@ -1173,7 +1173,9 @@
       <c r="K3" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="25"/>
+      <c r="L3" s="20" t="s">
+        <v>47</v>
+      </c>
       <c r="M3" s="25" t="s">
         <v>28</v>
       </c>
@@ -1258,7 +1260,7 @@
         <v>34</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M5" s="28" t="s">
         <v>35</v>
@@ -1300,7 +1302,9 @@
       <c r="K6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="28"/>
+      <c r="L6" s="28" t="s">
+        <v>51</v>
+      </c>
       <c r="M6" s="28" t="s">
         <v>38</v>
       </c>
@@ -1383,7 +1387,7 @@
         <v>43</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M8" s="28" t="s">
         <v>44</v>
@@ -1426,7 +1430,7 @@
         <v>46</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M9" s="28" t="s">
         <v>44</v>
@@ -1466,7 +1470,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="L2" r:id="rId1" display="https://www.flickr.com/photos/139186991@N03/53098748328/in/dateposted-public/" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L3" r:id="rId1" display="https://www.flickr.com/photos/139186991@N03/53098748328/in/dateposted-public/" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="S3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="L4" r:id="rId3" display="https://www.flickr.com/photos/197507288@N06/53136362437/in/dateposted-public/" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="L5" r:id="rId4" display="https://www.flickr.com/photos/139186991@N03/53098462054/in/dateposted-public/" xr:uid="{00000000-0004-0000-0000-000003000000}"/>

--- a/figures/timeline-sea/TimelineJS3 Template_Seattle DWO_May 2026.xlsx
+++ b/figures/timeline-sea/TimelineJS3 Template_Seattle DWO_May 2026.xlsx
@@ -1,25 +1,39 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lians\git\dwbr-website\figures\timeline-sea\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64306BEA-21FB-436A-A8AD-3FB5B0DD219D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="od1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>Worksheets</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>od1</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <cp:lastModifiedBy>Li-An Song</cp:lastModifiedBy>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-05-27T22:53:24Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
@@ -253,7 +267,7 @@
 </comments>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>Year</t>
@@ -349,10 +363,10 @@
     <t>Getting the word out</t>
   </si>
   <si>
-    <t>During May a series of actions occurred to highlight key elements of the Domestic Workers Ordinance. These included &lt;a href="https:/domesticemployers.org/"&gt;Hand in Hand: The Domestic Employer Network&lt;/a&gt; holding webinars to introduce employers to the campaign for the DWBR, among other events aimed at domestic workers.</t>
-  </si>
-  <si>
-    <t>Media Credit: Hand In Hand: The Domestic Worker Network</t>
+    <t>During May a series of actions occurred to highlight key elements of the Domestic Workers Ordinance. These included &lt;a href="https:/domesticemployers.org/"&gt;Hand in Hand: The Domestic Employers Network&lt;/a&gt; holding webinars to introduce employers to the campaign for the DWBR, among other events aimed at domestic workers.</t>
+  </si>
+  <si>
+    <t>Media Credit: Hand In Hand: The Domestic Employers Network</t>
   </si>
   <si>
     <t>The Domestic Workers Ordinance is introduced and passes in Committee</t>
@@ -417,7 +431,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.###############"/>
@@ -708,7 +722,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1023,7 +1037,27 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lians\git\dwbr-website\figures\timeline-sea\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64306BEA-21FB-436A-A8AD-3FB5B0DD219D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="od1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
